--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2021.xlsx
@@ -67,24 +67,12 @@
     <t xml:space="preserve">Valor (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11202</t>
   </si>
   <si>
     <t xml:space="preserve">Cisnes</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
@@ -988,6 +976,12 @@
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">6108</t>
   </si>
   <si>
@@ -1357,6 +1351,12 @@
     <t xml:space="preserve">Freirina</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">3202</t>
   </si>
   <si>
@@ -2086,7 +2086,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:26</t>
+    <t xml:space="preserve">2026-09-09 20:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2598,7 +2598,7 @@
         <v>15</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>6.62</v>
+        <v>5.79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>15</v>
@@ -2630,7 +2630,7 @@
         <v>15</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>5.79</v>
+        <v>5.27</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>15</v>
@@ -2662,7 +2662,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>5.67</v>
+        <v>4.12</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>15</v>
@@ -2694,7 +2694,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>5.27</v>
+        <v>3.78</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>15</v>
@@ -2726,7 +2726,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4.12</v>
+        <v>3.76</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>15</v>
@@ -2758,7 +2758,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>15</v>
@@ -2769,16 +2769,16 @@
         <v>2021</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2790,7 +2790,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>3.76</v>
+        <v>3.57</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>15</v>
@@ -2801,16 +2801,16 @@
         <v>2021</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -2822,7 +2822,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>3.74</v>
+        <v>3.45</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>15</v>
@@ -2836,7 +2836,7 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>33</v>
@@ -2854,7 +2854,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>15</v>
@@ -2868,7 +2868,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>35</v>
@@ -2886,7 +2886,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>3.45</v>
+        <v>3.09</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>15</v>
@@ -2900,7 +2900,7 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>37</v>
@@ -2918,7 +2918,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>15</v>
@@ -2932,7 +2932,7 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>39</v>
@@ -2950,7 +2950,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>3.09</v>
+        <v>1.57</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>15</v>
@@ -2964,7 +2964,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>41</v>
@@ -2982,7 +2982,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>15</v>
@@ -2993,28 +2993,28 @@
         <v>2021</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1.57</v>
+        <v>6.63</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>15</v>
@@ -3025,28 +3025,28 @@
         <v>2021</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>15</v>
@@ -3057,28 +3057,28 @@
         <v>2021</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>6.63</v>
+        <v>6.37</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>15</v>
@@ -3089,28 +3089,28 @@
         <v>2021</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>6.6</v>
+        <v>6.31</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>15</v>
@@ -3124,7 +3124,7 @@
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>56</v>
@@ -3133,16 +3133,16 @@
         <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>6.37</v>
+        <v>6.23</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>15</v>
@@ -3153,10 +3153,10 @@
         <v>2021</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>58</v>
@@ -3165,16 +3165,16 @@
         <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>6.31</v>
+        <v>6.17</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>15</v>
@@ -3185,28 +3185,28 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>6.23</v>
+        <v>6.11</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>15</v>
@@ -3220,25 +3220,25 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>6.17</v>
+        <v>6.02</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>15</v>
@@ -3249,10 +3249,10 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>65</v>
@@ -3261,16 +3261,16 @@
         <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>6.11</v>
+        <v>5.9</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>15</v>
@@ -3284,7 +3284,7 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>67</v>
@@ -3293,16 +3293,16 @@
         <v>68</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>6.02</v>
+        <v>5.86</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>15</v>
@@ -3313,10 +3313,10 @@
         <v>2021</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>69</v>
@@ -3325,16 +3325,16 @@
         <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>5.9</v>
+        <v>5.64</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>15</v>
@@ -3348,7 +3348,7 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>71</v>
@@ -3357,16 +3357,16 @@
         <v>72</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>5.86</v>
+        <v>5.62</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>15</v>
@@ -3377,10 +3377,10 @@
         <v>2021</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>73</v>
@@ -3389,16 +3389,16 @@
         <v>74</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>5.64</v>
+        <v>5.6</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>15</v>
@@ -3409,10 +3409,10 @@
         <v>2021</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>75</v>
@@ -3421,16 +3421,16 @@
         <v>76</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>5.62</v>
+        <v>5.58</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>15</v>
@@ -3441,10 +3441,10 @@
         <v>2021</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>77</v>
@@ -3453,16 +3453,16 @@
         <v>78</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>5.6</v>
+        <v>5.52</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>15</v>
@@ -3476,7 +3476,7 @@
         <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>79</v>
@@ -3485,16 +3485,16 @@
         <v>80</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>5.58</v>
+        <v>5.48</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>15</v>
@@ -3508,7 +3508,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>81</v>
@@ -3517,16 +3517,16 @@
         <v>82</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>5.52</v>
+        <v>5.47</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>15</v>
@@ -3537,10 +3537,10 @@
         <v>2021</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>83</v>
@@ -3549,16 +3549,16 @@
         <v>84</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>5.48</v>
+        <v>5.46</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>15</v>
@@ -3569,10 +3569,10 @@
         <v>2021</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>85</v>
@@ -3581,16 +3581,16 @@
         <v>86</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>5.47</v>
+        <v>5.41</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>15</v>
@@ -3604,7 +3604,7 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>87</v>
@@ -3613,16 +3613,16 @@
         <v>88</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>5.46</v>
+        <v>5.39</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>15</v>
@@ -3636,7 +3636,7 @@
         <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>89</v>
@@ -3645,16 +3645,16 @@
         <v>90</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>5.41</v>
+        <v>5.33</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>15</v>
@@ -3668,7 +3668,7 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>91</v>
@@ -3677,16 +3677,16 @@
         <v>92</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>5.39</v>
+        <v>5.31</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>15</v>
@@ -3700,7 +3700,7 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>93</v>
@@ -3709,16 +3709,16 @@
         <v>94</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>5.33</v>
+        <v>5.27</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>15</v>
@@ -3732,7 +3732,7 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>95</v>
@@ -3741,16 +3741,16 @@
         <v>96</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>5.31</v>
+        <v>5.2</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>15</v>
@@ -3761,10 +3761,10 @@
         <v>2021</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>97</v>
@@ -3773,16 +3773,16 @@
         <v>98</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>5.27</v>
+        <v>5.18</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>15</v>
@@ -3793,10 +3793,10 @@
         <v>2021</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>99</v>
@@ -3805,16 +3805,16 @@
         <v>100</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>5.2</v>
+        <v>5.16</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>15</v>
@@ -3825,10 +3825,10 @@
         <v>2021</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>101</v>
@@ -3837,16 +3837,16 @@
         <v>102</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>5.18</v>
+        <v>5.14</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>15</v>
@@ -3857,10 +3857,10 @@
         <v>2021</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>103</v>
@@ -3869,16 +3869,16 @@
         <v>104</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>5.16</v>
+        <v>5.03</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>15</v>
@@ -3892,7 +3892,7 @@
         <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>105</v>
@@ -3901,16 +3901,16 @@
         <v>106</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>5.14</v>
+        <v>5.01</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>15</v>
@@ -3921,10 +3921,10 @@
         <v>2021</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>107</v>
@@ -3933,16 +3933,16 @@
         <v>108</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>5.03</v>
+        <v>5.01</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>15</v>
@@ -3953,10 +3953,10 @@
         <v>2021</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>109</v>
@@ -3965,16 +3965,16 @@
         <v>110</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>5.01</v>
+        <v>4.99</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>15</v>
@@ -3985,10 +3985,10 @@
         <v>2021</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>111</v>
@@ -3997,16 +3997,16 @@
         <v>112</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>5.01</v>
+        <v>4.99</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>15</v>
@@ -4017,10 +4017,10 @@
         <v>2021</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>113</v>
@@ -4029,16 +4029,16 @@
         <v>114</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -4052,7 +4052,7 @@
         <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>115</v>
@@ -4061,16 +4061,16 @@
         <v>116</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>4.99</v>
+        <v>4.96</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>15</v>
@@ -4081,10 +4081,10 @@
         <v>2021</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>117</v>
@@ -4093,10 +4093,10 @@
         <v>118</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4116,7 +4116,7 @@
         <v>13</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4125,16 +4125,16 @@
         <v>120</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>4.96</v>
+        <v>4.87</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>15</v>
@@ -4145,10 +4145,10 @@
         <v>2021</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>121</v>
@@ -4157,16 +4157,16 @@
         <v>122</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>4.96</v>
+        <v>4.84</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>15</v>
@@ -4177,10 +4177,10 @@
         <v>2021</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>123</v>
@@ -4189,16 +4189,16 @@
         <v>124</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>4.87</v>
+        <v>4.84</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>15</v>
@@ -4209,10 +4209,10 @@
         <v>2021</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>125</v>
@@ -4221,16 +4221,16 @@
         <v>126</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>4.84</v>
+        <v>4.83</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>15</v>
@@ -4241,10 +4241,10 @@
         <v>2021</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>127</v>
@@ -4253,16 +4253,16 @@
         <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>4.84</v>
+        <v>4.82</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>15</v>
@@ -4273,28 +4273,28 @@
         <v>2021</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>4.83</v>
+        <v>4.81</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>15</v>
@@ -4308,25 +4308,25 @@
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -4337,10 +4337,10 @@
         <v>2021</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>134</v>
@@ -4349,16 +4349,16 @@
         <v>135</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>4.81</v>
+        <v>4.75</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>15</v>
@@ -4369,10 +4369,10 @@
         <v>2021</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>136</v>
@@ -4381,16 +4381,16 @@
         <v>137</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>4.78</v>
+        <v>4.72</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>15</v>
@@ -4401,10 +4401,10 @@
         <v>2021</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>138</v>
@@ -4413,16 +4413,16 @@
         <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>15</v>
@@ -4436,7 +4436,7 @@
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>140</v>
@@ -4445,16 +4445,16 @@
         <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>4.72</v>
+        <v>4.67</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>15</v>
@@ -4468,7 +4468,7 @@
         <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4477,16 +4477,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>15</v>
@@ -4500,7 +4500,7 @@
         <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4509,16 +4509,16 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>4.67</v>
+        <v>4.58</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>15</v>
@@ -4529,10 +4529,10 @@
         <v>2021</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4541,16 +4541,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>4.62</v>
+        <v>4.54</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>15</v>
@@ -4561,10 +4561,10 @@
         <v>2021</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4573,16 +4573,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>15</v>
@@ -4593,10 +4593,10 @@
         <v>2021</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4605,16 +4605,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>4.54</v>
+        <v>4.49</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>15</v>
@@ -4625,10 +4625,10 @@
         <v>2021</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4637,16 +4637,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>15</v>
@@ -4657,10 +4657,10 @@
         <v>2021</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4669,16 +4669,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>4.49</v>
+        <v>4.44</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>15</v>
@@ -4689,10 +4689,10 @@
         <v>2021</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4701,16 +4701,16 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>15</v>
@@ -4724,7 +4724,7 @@
         <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4733,16 +4733,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>15</v>
@@ -4753,10 +4753,10 @@
         <v>2021</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4765,16 +4765,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>4.44</v>
+        <v>4.33</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>15</v>
@@ -4788,7 +4788,7 @@
         <v>13</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4797,16 +4797,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>15</v>
@@ -4817,10 +4817,10 @@
         <v>2021</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4829,16 +4829,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>15</v>
@@ -4849,10 +4849,10 @@
         <v>2021</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4861,16 +4861,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4881,10 +4881,10 @@
         <v>2021</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4893,16 +4893,16 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>15</v>
@@ -4916,7 +4916,7 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4925,16 +4925,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>15</v>
@@ -4945,10 +4945,10 @@
         <v>2021</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -4957,16 +4957,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>15</v>
@@ -4977,10 +4977,10 @@
         <v>2021</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -4989,16 +4989,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>15</v>
@@ -5009,10 +5009,10 @@
         <v>2021</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>176</v>
@@ -5021,16 +5021,16 @@
         <v>177</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>15</v>
@@ -5044,7 +5044,7 @@
         <v>13</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>178</v>
@@ -5053,16 +5053,16 @@
         <v>179</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>15</v>
@@ -5073,10 +5073,10 @@
         <v>2021</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>180</v>
@@ -5085,16 +5085,16 @@
         <v>181</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>15</v>
@@ -5105,10 +5105,10 @@
         <v>2021</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>182</v>
@@ -5117,16 +5117,16 @@
         <v>183</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>4.21</v>
+        <v>4.19</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>15</v>
@@ -5137,10 +5137,10 @@
         <v>2021</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>184</v>
@@ -5149,16 +5149,16 @@
         <v>185</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>15</v>
@@ -5169,10 +5169,10 @@
         <v>2021</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>186</v>
@@ -5181,16 +5181,16 @@
         <v>187</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>15</v>
@@ -5201,10 +5201,10 @@
         <v>2021</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>188</v>
@@ -5213,10 +5213,10 @@
         <v>189</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5233,10 +5233,10 @@
         <v>2021</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>190</v>
@@ -5245,10 +5245,10 @@
         <v>191</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5265,10 +5265,10 @@
         <v>2021</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>192</v>
@@ -5277,16 +5277,16 @@
         <v>193</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>15</v>
@@ -5297,10 +5297,10 @@
         <v>2021</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>194</v>
@@ -5309,16 +5309,16 @@
         <v>195</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>15</v>
@@ -5329,10 +5329,10 @@
         <v>2021</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>196</v>
@@ -5341,16 +5341,16 @@
         <v>197</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>4.15</v>
+        <v>4.11</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>15</v>
@@ -5361,10 +5361,10 @@
         <v>2021</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>198</v>
@@ -5373,16 +5373,16 @@
         <v>199</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>4.15</v>
+        <v>4.09</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>15</v>
@@ -5393,10 +5393,10 @@
         <v>2021</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>200</v>
@@ -5405,16 +5405,16 @@
         <v>201</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>15</v>
@@ -5425,10 +5425,10 @@
         <v>2021</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>202</v>
@@ -5437,16 +5437,16 @@
         <v>203</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>4.09</v>
+        <v>4.07</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>15</v>
@@ -5460,7 +5460,7 @@
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>204</v>
@@ -5469,16 +5469,16 @@
         <v>205</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>15</v>
@@ -5489,10 +5489,10 @@
         <v>2021</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>206</v>
@@ -5501,16 +5501,16 @@
         <v>207</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>4.07</v>
+        <v>3.99</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>15</v>
@@ -5521,10 +5521,10 @@
         <v>2021</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>208</v>
@@ -5533,16 +5533,16 @@
         <v>209</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>4.04</v>
+        <v>3.99</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>15</v>
@@ -5556,7 +5556,7 @@
         <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>210</v>
@@ -5565,16 +5565,16 @@
         <v>211</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>3.99</v>
+        <v>3.98</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>15</v>
@@ -5588,7 +5588,7 @@
         <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>212</v>
@@ -5597,16 +5597,16 @@
         <v>213</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>3.99</v>
+        <v>3.95</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>15</v>
@@ -5620,7 +5620,7 @@
         <v>13</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>214</v>
@@ -5629,16 +5629,16 @@
         <v>215</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>15</v>
@@ -5649,10 +5649,10 @@
         <v>2021</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>216</v>
@@ -5661,16 +5661,16 @@
         <v>217</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>15</v>
@@ -5684,7 +5684,7 @@
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5693,16 +5693,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>15</v>
@@ -5716,7 +5716,7 @@
         <v>16</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5725,16 +5725,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>15</v>
@@ -5745,10 +5745,10 @@
         <v>2021</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5757,16 +5757,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>15</v>
@@ -5780,7 +5780,7 @@
         <v>16</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5789,16 +5789,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>15</v>
@@ -5809,10 +5809,10 @@
         <v>2021</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5821,16 +5821,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>15</v>
@@ -5841,10 +5841,10 @@
         <v>2021</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5853,16 +5853,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>15</v>
@@ -5873,10 +5873,10 @@
         <v>2021</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5885,16 +5885,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5905,10 +5905,10 @@
         <v>2021</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5917,16 +5917,16 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>3.88</v>
+        <v>3.85</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>15</v>
@@ -5937,10 +5937,10 @@
         <v>2021</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5949,16 +5949,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>15</v>
@@ -5969,10 +5969,10 @@
         <v>2021</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -5981,16 +5981,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>3.85</v>
+        <v>3.83</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>15</v>
@@ -6001,10 +6001,10 @@
         <v>2021</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -6013,16 +6013,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>15</v>
@@ -6033,10 +6033,10 @@
         <v>2021</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6045,16 +6045,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>3.83</v>
+        <v>3.76</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>15</v>
@@ -6065,10 +6065,10 @@
         <v>2021</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>133</v>
+        <v>43</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6077,16 +6077,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>15</v>
@@ -6100,7 +6100,7 @@
         <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6109,16 +6109,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>15</v>
@@ -6129,10 +6129,10 @@
         <v>2021</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6141,16 +6141,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>15</v>
@@ -6161,10 +6161,10 @@
         <v>2021</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6173,10 +6173,10 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6193,10 +6193,10 @@
         <v>2021</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6205,16 +6205,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>15</v>
@@ -6225,10 +6225,10 @@
         <v>2021</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6237,16 +6237,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>15</v>
@@ -6257,10 +6257,10 @@
         <v>2021</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6269,16 +6269,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>15</v>
@@ -6289,10 +6289,10 @@
         <v>2021</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6301,16 +6301,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>15</v>
@@ -6324,7 +6324,7 @@
         <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6333,16 +6333,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>3.69</v>
+        <v>3.55</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>15</v>
@@ -6356,7 +6356,7 @@
         <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6365,16 +6365,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>15</v>
@@ -6385,10 +6385,10 @@
         <v>2021</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6397,16 +6397,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>15</v>
@@ -6417,10 +6417,10 @@
         <v>2021</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6429,16 +6429,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>15</v>
@@ -6449,10 +6449,10 @@
         <v>2021</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6461,16 +6461,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>15</v>
@@ -6481,10 +6481,10 @@
         <v>2021</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6493,16 +6493,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>3.53</v>
+        <v>3.5</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>15</v>
@@ -6516,7 +6516,7 @@
         <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6525,16 +6525,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>3.5</v>
+        <v>3.47</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>15</v>
@@ -6545,10 +6545,10 @@
         <v>2021</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6557,16 +6557,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>15</v>
@@ -6577,10 +6577,10 @@
         <v>2021</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6589,16 +6589,16 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>3.47</v>
+        <v>3.43</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>15</v>
@@ -6609,10 +6609,10 @@
         <v>2021</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6621,16 +6621,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>15</v>
@@ -6641,10 +6641,10 @@
         <v>2021</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6653,16 +6653,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>3.43</v>
+        <v>3.4</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>15</v>
@@ -6676,7 +6676,7 @@
         <v>6</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6685,16 +6685,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>15</v>
@@ -6705,10 +6705,10 @@
         <v>2021</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>55</v>
+        <v>129</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6717,16 +6717,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6737,10 +6737,10 @@
         <v>2021</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6749,16 +6749,16 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>15</v>
@@ -6769,10 +6769,10 @@
         <v>2021</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6781,16 +6781,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>15</v>
@@ -6801,10 +6801,10 @@
         <v>2021</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6813,16 +6813,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>15</v>
@@ -6833,10 +6833,10 @@
         <v>2021</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6845,16 +6845,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>15</v>
@@ -6865,10 +6865,10 @@
         <v>2021</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6877,16 +6877,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>15</v>
@@ -6897,10 +6897,10 @@
         <v>2021</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6909,16 +6909,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>15</v>
@@ -6929,10 +6929,10 @@
         <v>2021</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6941,16 +6941,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>15</v>
@@ -6961,10 +6961,10 @@
         <v>2021</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -6973,16 +6973,16 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>15</v>
@@ -6993,10 +6993,10 @@
         <v>2021</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -7005,16 +7005,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>15</v>
@@ -7025,10 +7025,10 @@
         <v>2021</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7037,16 +7037,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>15</v>
@@ -7057,28 +7057,28 @@
         <v>2021</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>305</v>
+        <v>43</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>15</v>
@@ -7089,28 +7089,28 @@
         <v>2021</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D144" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E144" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="E144" s="2" t="s">
-        <v>307</v>
-      </c>
       <c r="F144" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>15</v>
@@ -7121,28 +7121,28 @@
         <v>2021</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D145" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E145" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="E145" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="F145" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>15</v>
@@ -7153,10 +7153,10 @@
         <v>2021</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>309</v>
@@ -7165,16 +7165,16 @@
         <v>310</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>15</v>
@@ -7185,10 +7185,10 @@
         <v>2021</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>311</v>
@@ -7197,16 +7197,16 @@
         <v>312</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>15</v>
@@ -7217,10 +7217,10 @@
         <v>2021</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>313</v>
@@ -7229,16 +7229,16 @@
         <v>314</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>3.19</v>
+        <v>3.16</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>15</v>
@@ -7249,10 +7249,10 @@
         <v>2021</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>315</v>
@@ -7261,16 +7261,16 @@
         <v>316</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>15</v>
@@ -7281,10 +7281,10 @@
         <v>2021</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>317</v>
@@ -7293,16 +7293,16 @@
         <v>318</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>15</v>
@@ -7313,10 +7313,10 @@
         <v>2021</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>319</v>
@@ -7325,16 +7325,16 @@
         <v>320</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>15</v>
@@ -7345,10 +7345,10 @@
         <v>2021</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>321</v>
@@ -7357,16 +7357,16 @@
         <v>322</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>15</v>
@@ -7377,10 +7377,10 @@
         <v>2021</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>323</v>
@@ -7389,16 +7389,16 @@
         <v>324</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>15</v>
@@ -7409,10 +7409,10 @@
         <v>2021</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>325</v>
@@ -7421,16 +7421,16 @@
         <v>326</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>15</v>
@@ -7441,10 +7441,10 @@
         <v>2021</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>327</v>
@@ -7453,16 +7453,16 @@
         <v>328</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>15</v>
@@ -7473,10 +7473,10 @@
         <v>2021</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>329</v>
@@ -7485,16 +7485,16 @@
         <v>330</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>15</v>
@@ -7505,10 +7505,10 @@
         <v>2021</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>331</v>
@@ -7517,16 +7517,16 @@
         <v>332</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>15</v>
@@ -7537,10 +7537,10 @@
         <v>2021</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>333</v>
@@ -7549,16 +7549,16 @@
         <v>334</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>15</v>
@@ -7569,10 +7569,10 @@
         <v>2021</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>335</v>
@@ -7581,16 +7581,16 @@
         <v>336</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>15</v>
@@ -7601,10 +7601,10 @@
         <v>2021</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>337</v>
@@ -7613,16 +7613,16 @@
         <v>338</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>15</v>
@@ -7636,7 +7636,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>339</v>
@@ -7645,16 +7645,16 @@
         <v>340</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>15</v>
@@ -7668,7 +7668,7 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>341</v>
@@ -7677,16 +7677,16 @@
         <v>342</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>15</v>
@@ -7697,10 +7697,10 @@
         <v>2021</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>343</v>
@@ -7709,10 +7709,10 @@
         <v>344</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7729,10 +7729,10 @@
         <v>2021</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7741,16 +7741,16 @@
         <v>346</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>15</v>
@@ -7761,10 +7761,10 @@
         <v>2021</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>347</v>
@@ -7773,16 +7773,16 @@
         <v>348</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>15</v>
@@ -7793,10 +7793,10 @@
         <v>2021</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>349</v>
@@ -7805,16 +7805,16 @@
         <v>350</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>15</v>
@@ -7825,10 +7825,10 @@
         <v>2021</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>351</v>
@@ -7837,16 +7837,16 @@
         <v>352</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>15</v>
@@ -7857,10 +7857,10 @@
         <v>2021</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>353</v>
@@ -7869,16 +7869,16 @@
         <v>354</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>15</v>
@@ -7889,10 +7889,10 @@
         <v>2021</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>355</v>
@@ -7901,16 +7901,16 @@
         <v>356</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>15</v>
@@ -7921,10 +7921,10 @@
         <v>2021</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -7933,16 +7933,16 @@
         <v>358</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>2.27</v>
+        <v>2.14</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>15</v>
@@ -7953,10 +7953,10 @@
         <v>2021</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -7965,16 +7965,16 @@
         <v>360</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>15</v>
@@ -7985,10 +7985,10 @@
         <v>2021</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -7997,16 +7997,16 @@
         <v>362</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>15</v>
@@ -8017,10 +8017,10 @@
         <v>2021</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8029,10 +8029,10 @@
         <v>364</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8052,7 +8052,7 @@
         <v>6</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8061,16 +8061,16 @@
         <v>366</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -8081,10 +8081,10 @@
         <v>2021</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8093,16 +8093,16 @@
         <v>368</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>15</v>
@@ -8116,7 +8116,7 @@
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8125,16 +8125,16 @@
         <v>370</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>15</v>
@@ -8145,10 +8145,10 @@
         <v>2021</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>52</v>
+        <v>129</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>371</v>
@@ -8157,16 +8157,16 @@
         <v>372</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>15</v>
@@ -8180,7 +8180,7 @@
         <v>16</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8189,16 +8189,16 @@
         <v>374</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>15</v>
@@ -8212,7 +8212,7 @@
         <v>16</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8221,16 +8221,16 @@
         <v>376</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>15</v>
@@ -8241,10 +8241,10 @@
         <v>2021</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>133</v>
+        <v>48</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8253,16 +8253,16 @@
         <v>378</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>15</v>
@@ -8276,7 +8276,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8285,16 +8285,16 @@
         <v>380</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>15</v>
@@ -8305,28 +8305,28 @@
         <v>2021</v>
       </c>
       <c r="B182" s="2" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>52</v>
+        <v>381</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>50</v>
+        <v>384</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>51</v>
+        <v>385</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>0.96</v>
+        <v>8.82</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>15</v>
@@ -8337,28 +8337,28 @@
         <v>2021</v>
       </c>
       <c r="B183" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D183" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="F183" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="E183" s="2" t="s">
+      <c r="G183" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="F183" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="G183" s="2" t="s">
-        <v>387</v>
-      </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>8.82</v>
+        <v>6.83</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>15</v>
@@ -8369,10 +8369,10 @@
         <v>2021</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>389</v>
@@ -8381,16 +8381,16 @@
         <v>390</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>6.83</v>
+        <v>6.09</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>15</v>
@@ -8401,10 +8401,10 @@
         <v>2021</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>391</v>
@@ -8413,16 +8413,16 @@
         <v>392</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>6.09</v>
+        <v>6.03</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>15</v>
@@ -8433,28 +8433,28 @@
         <v>2021</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>6.03</v>
+        <v>5.43</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>15</v>
@@ -8465,28 +8465,28 @@
         <v>2021</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>5.43</v>
+        <v>5.18</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>15</v>
@@ -8500,7 +8500,7 @@
         <v>4</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>399</v>
@@ -8509,16 +8509,16 @@
         <v>400</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>5.18</v>
+        <v>5.14</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>15</v>
@@ -8529,10 +8529,10 @@
         <v>2021</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>401</v>
@@ -8541,16 +8541,16 @@
         <v>402</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>5.14</v>
+        <v>5.04</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>15</v>
@@ -8561,10 +8561,10 @@
         <v>2021</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>403</v>
@@ -8573,16 +8573,16 @@
         <v>404</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>15</v>
@@ -8593,10 +8593,10 @@
         <v>2021</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>405</v>
@@ -8605,16 +8605,16 @@
         <v>406</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>15</v>
@@ -8625,10 +8625,10 @@
         <v>2021</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>407</v>
@@ -8637,16 +8637,16 @@
         <v>408</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>4.94</v>
+        <v>4.93</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>15</v>
@@ -8657,28 +8657,28 @@
         <v>2021</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>4.93</v>
+        <v>4.76</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>15</v>
@@ -8689,10 +8689,10 @@
         <v>2021</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>412</v>
@@ -8701,10 +8701,10 @@
         <v>413</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8721,10 +8721,10 @@
         <v>2021</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>414</v>
@@ -8733,16 +8733,16 @@
         <v>415</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>4.76</v>
+        <v>4.69</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>15</v>
@@ -8756,7 +8756,7 @@
         <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>416</v>
@@ -8765,16 +8765,16 @@
         <v>417</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>4.69</v>
+        <v>4.19</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>15</v>
@@ -8785,10 +8785,10 @@
         <v>2021</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>395</v>
+        <v>381</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>418</v>
@@ -8797,16 +8797,16 @@
         <v>419</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>4.19</v>
+        <v>4.01</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>15</v>
@@ -8817,10 +8817,10 @@
         <v>2021</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>420</v>
@@ -8829,16 +8829,16 @@
         <v>421</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>4.01</v>
+        <v>3.97</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>15</v>
@@ -8849,10 +8849,10 @@
         <v>2021</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>422</v>
@@ -8861,16 +8861,16 @@
         <v>423</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>3.97</v>
+        <v>3.91</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>15</v>
@@ -8881,28 +8881,28 @@
         <v>2021</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>424</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>425</v>
+        <v>381</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>3.91</v>
+        <v>3.89</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>15</v>
@@ -8916,25 +8916,25 @@
         <v>2</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D201" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E201" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="E201" s="2" t="s">
-        <v>383</v>
-      </c>
       <c r="F201" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>3.89</v>
+        <v>3.87</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>15</v>
@@ -8945,28 +8945,28 @@
         <v>2021</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>427</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>428</v>
+        <v>396</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>15</v>
@@ -8980,25 +8980,25 @@
         <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D203" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E203" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="E203" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="F203" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>3.86</v>
+        <v>3.82</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>15</v>
@@ -9009,10 +9009,10 @@
         <v>2021</v>
       </c>
       <c r="B204" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>430</v>
@@ -9021,16 +9021,16 @@
         <v>431</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>3.82</v>
+        <v>3.64</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>15</v>
@@ -9041,10 +9041,10 @@
         <v>2021</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>432</v>
@@ -9053,16 +9053,16 @@
         <v>433</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>3.64</v>
+        <v>3.54</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>15</v>
@@ -9073,10 +9073,10 @@
         <v>2021</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>434</v>
@@ -9085,16 +9085,16 @@
         <v>435</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>3.54</v>
+        <v>3.48</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>15</v>
@@ -9108,7 +9108,7 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>436</v>
@@ -9117,16 +9117,16 @@
         <v>437</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>3.48</v>
+        <v>3.26</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>15</v>
@@ -9137,10 +9137,10 @@
         <v>2021</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>438</v>
@@ -9149,16 +9149,16 @@
         <v>439</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>3.26</v>
+        <v>3.16</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>15</v>
@@ -9169,10 +9169,10 @@
         <v>2021</v>
       </c>
       <c r="B209" s="2" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>411</v>
+        <v>381</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>440</v>
@@ -9181,16 +9181,16 @@
         <v>441</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>15</v>
@@ -9201,10 +9201,10 @@
         <v>2021</v>
       </c>
       <c r="B210" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>442</v>
@@ -9213,16 +9213,16 @@
         <v>443</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>15</v>
@@ -9233,10 +9233,10 @@
         <v>2021</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>444</v>
@@ -9245,16 +9245,16 @@
         <v>445</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>15</v>
@@ -9268,7 +9268,7 @@
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>446</v>
@@ -9277,10 +9277,10 @@
         <v>447</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9300,7 +9300,7 @@
         <v>3</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>448</v>
@@ -9309,10 +9309,10 @@
         <v>449</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9332,7 +9332,7 @@
         <v>3</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>450</v>
@@ -9341,10 +9341,10 @@
         <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9364,7 +9364,7 @@
         <v>4</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>452</v>
@@ -9373,10 +9373,10 @@
         <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9396,7 +9396,7 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>454</v>
@@ -9405,10 +9405,10 @@
         <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9428,7 +9428,7 @@
         <v>2</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>456</v>
@@ -9437,10 +9437,10 @@
         <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9460,7 +9460,7 @@
         <v>4</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>458</v>
@@ -9469,10 +9469,10 @@
         <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9492,7 +9492,7 @@
         <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>460</v>
@@ -9501,10 +9501,10 @@
         <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9524,7 +9524,7 @@
         <v>4</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>462</v>
@@ -9533,10 +9533,10 @@
         <v>463</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9556,7 +9556,7 @@
         <v>4</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>464</v>
@@ -9565,10 +9565,10 @@
         <v>465</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9588,7 +9588,7 @@
         <v>2</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>466</v>
@@ -9597,10 +9597,10 @@
         <v>467</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9620,7 +9620,7 @@
         <v>1</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>468</v>
@@ -9629,10 +9629,10 @@
         <v>469</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2021.xlsx
@@ -1849,18 +1849,18 @@
     <t xml:space="preserve">Cañete</t>
   </si>
   <si>
+    <t xml:space="preserve">8205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curanilahue</t>
+  </si>
+  <si>
     <t xml:space="preserve">8302</t>
   </si>
   <si>
     <t xml:space="preserve">Antuco</t>
   </si>
   <si>
-    <t xml:space="preserve">8205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curanilahue</t>
-  </si>
-  <si>
     <t xml:space="preserve">9203</t>
   </si>
   <si>
@@ -2086,7 +2086,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:19</t>
+    <t xml:space="preserve">2026-09-18 11:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_rezmat_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_rezmat_a_2021.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="707">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">metric_label</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">11401</t>
@@ -70,9 +70,6 @@
     <t xml:space="preserve">11201</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">11202</t>
   </si>
   <si>
@@ -184,7 +181,7 @@
     <t xml:space="preserve">La Pintana</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">5107</t>
@@ -277,9 +274,6 @@
     <t xml:space="preserve">5101</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">5706</t>
   </si>
   <si>
@@ -418,7 +412,7 @@
     <t xml:space="preserve">Isla de Maipo</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">16106</t>
@@ -1189,7 +1183,7 @@
     <t xml:space="preserve">Macrozona Norte</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">1403</t>
@@ -1441,7 +1435,7 @@
     <t xml:space="preserve">Camiña</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">8314</t>
@@ -1477,7 +1471,7 @@
     <t xml:space="preserve">San Juan de la Costa</t>
   </si>
   <si>
-    <t xml:space="preserve">La Araucania</t>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">9207</t>
@@ -1534,7 +1528,7 @@
     <t xml:space="preserve">San Pablo</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">14102</t>
@@ -1738,7 +1732,7 @@
     <t xml:space="preserve">8206</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">9109</t>
@@ -1888,7 +1882,7 @@
     <t xml:space="preserve">8301</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">10109</t>
@@ -2098,7 +2092,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-10-05 18:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2598,7 +2592,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>13</v>
@@ -2627,10 +2621,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>13</v>
@@ -2659,10 +2653,10 @@
         <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
@@ -2691,10 +2685,10 @@
         <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>13</v>
@@ -2723,10 +2717,10 @@
         <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -2755,10 +2749,10 @@
         <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
@@ -2787,10 +2781,10 @@
         <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2819,10 +2813,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -2848,13 +2842,13 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="E11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -2880,13 +2874,13 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>13</v>
@@ -2912,13 +2906,13 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -2944,13 +2938,13 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
@@ -2976,13 +2970,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -3008,13 +3002,13 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -3040,13 +3034,13 @@
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -3072,19 +3066,19 @@
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="F18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
@@ -3104,19 +3098,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -3136,19 +3130,19 @@
         <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="E20" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -3168,19 +3162,19 @@
         <v>5</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -3200,19 +3194,19 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -3232,19 +3226,19 @@
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -3264,19 +3258,19 @@
         <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -3296,19 +3290,19 @@
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -3328,19 +3322,19 @@
         <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -3360,19 +3354,19 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -3392,19 +3386,19 @@
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -3424,19 +3418,19 @@
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -3456,19 +3450,19 @@
         <v>6</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -3488,19 +3482,19 @@
         <v>13</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -3520,19 +3514,19 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -3552,19 +3546,19 @@
         <v>13</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -3584,19 +3578,19 @@
         <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -3616,19 +3610,19 @@
         <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -3648,19 +3642,19 @@
         <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -3680,19 +3674,19 @@
         <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -3712,19 +3706,19 @@
         <v>13</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3744,19 +3738,19 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -3776,19 +3770,19 @@
         <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3808,19 +3802,19 @@
         <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3840,19 +3834,19 @@
         <v>5</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3872,19 +3866,19 @@
         <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3904,19 +3898,19 @@
         <v>6</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -3936,19 +3930,19 @@
         <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -3968,19 +3962,19 @@
         <v>6</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -4000,19 +3994,19 @@
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -4032,19 +4026,19 @@
         <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -4064,19 +4058,19 @@
         <v>13</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -4096,19 +4090,19 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4128,19 +4122,19 @@
         <v>13</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4160,19 +4154,19 @@
         <v>13</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -4192,19 +4186,19 @@
         <v>13</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4224,19 +4218,19 @@
         <v>5</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4256,19 +4250,19 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4288,19 +4282,19 @@
         <v>7</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4320,19 +4314,19 @@
         <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -4352,19 +4346,19 @@
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -4384,19 +4378,19 @@
         <v>13</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4416,19 +4410,19 @@
         <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4448,19 +4442,19 @@
         <v>6</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4480,19 +4474,19 @@
         <v>5</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4512,19 +4506,19 @@
         <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4544,19 +4538,19 @@
         <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4576,19 +4570,19 @@
         <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -4608,19 +4602,19 @@
         <v>13</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -4640,19 +4634,19 @@
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -4672,19 +4666,19 @@
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -4704,19 +4698,19 @@
         <v>5</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4736,19 +4730,19 @@
         <v>13</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -4768,19 +4762,19 @@
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4800,19 +4794,19 @@
         <v>13</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -4832,19 +4826,19 @@
         <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -4864,19 +4858,19 @@
         <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4896,19 +4890,19 @@
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -4928,19 +4922,19 @@
         <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4960,19 +4954,19 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -4992,19 +4986,19 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -5024,19 +5018,19 @@
         <v>6</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5056,19 +5050,19 @@
         <v>13</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -5088,19 +5082,19 @@
         <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -5120,19 +5114,19 @@
         <v>13</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5152,19 +5146,19 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -5184,19 +5178,19 @@
         <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -5216,19 +5210,19 @@
         <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5248,19 +5242,19 @@
         <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5280,19 +5274,19 @@
         <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5312,19 +5306,19 @@
         <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5344,19 +5338,19 @@
         <v>13</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -5376,19 +5370,19 @@
         <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5408,19 +5402,19 @@
         <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5440,19 +5434,19 @@
         <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5472,19 +5466,19 @@
         <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5504,19 +5498,19 @@
         <v>6</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5536,19 +5530,19 @@
         <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -5568,19 +5562,19 @@
         <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5600,19 +5594,19 @@
         <v>13</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -5632,19 +5626,19 @@
         <v>13</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5664,19 +5658,19 @@
         <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5696,19 +5690,19 @@
         <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5728,19 +5722,19 @@
         <v>16</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5760,19 +5754,19 @@
         <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5792,19 +5786,19 @@
         <v>16</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5824,19 +5818,19 @@
         <v>6</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5856,19 +5850,19 @@
         <v>16</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5888,19 +5882,19 @@
         <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
@@ -5920,19 +5914,19 @@
         <v>7</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5952,19 +5946,19 @@
         <v>7</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -5984,19 +5978,19 @@
         <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -6016,19 +6010,19 @@
         <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -6048,19 +6042,19 @@
         <v>16</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6080,19 +6074,19 @@
         <v>16</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6112,19 +6106,19 @@
         <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -6144,19 +6138,19 @@
         <v>7</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6176,19 +6170,19 @@
         <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6208,19 +6202,19 @@
         <v>5</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6240,19 +6234,19 @@
         <v>6</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6272,19 +6266,19 @@
         <v>6</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -6304,19 +6298,19 @@
         <v>7</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6336,19 +6330,19 @@
         <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6368,19 +6362,19 @@
         <v>13</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6400,19 +6394,19 @@
         <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -6432,19 +6426,19 @@
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6464,19 +6458,19 @@
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6496,19 +6490,19 @@
         <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6528,19 +6522,19 @@
         <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6560,19 +6554,19 @@
         <v>7</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6592,19 +6586,19 @@
         <v>5</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6624,19 +6618,19 @@
         <v>16</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6656,19 +6650,19 @@
         <v>7</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6688,19 +6682,19 @@
         <v>6</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6720,19 +6714,19 @@
         <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -6752,19 +6746,19 @@
         <v>6</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6784,19 +6778,19 @@
         <v>16</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6816,19 +6810,19 @@
         <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6848,19 +6842,19 @@
         <v>6</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6880,19 +6874,19 @@
         <v>7</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6912,19 +6906,19 @@
         <v>7</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -6944,19 +6938,19 @@
         <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -6976,19 +6970,19 @@
         <v>6</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -7008,19 +7002,19 @@
         <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -7040,19 +7034,19 @@
         <v>7</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7072,19 +7066,19 @@
         <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -7104,19 +7098,19 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7136,19 +7130,19 @@
         <v>7</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7168,19 +7162,19 @@
         <v>16</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7200,19 +7194,19 @@
         <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -7232,19 +7226,19 @@
         <v>5</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7264,19 +7258,19 @@
         <v>6</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7296,19 +7290,19 @@
         <v>6</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7328,19 +7322,19 @@
         <v>16</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7360,19 +7354,19 @@
         <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7392,19 +7386,19 @@
         <v>6</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7424,19 +7418,19 @@
         <v>6</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7456,19 +7450,19 @@
         <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7488,19 +7482,19 @@
         <v>5</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7520,19 +7514,19 @@
         <v>6</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7552,19 +7546,19 @@
         <v>13</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7584,19 +7578,19 @@
         <v>6</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7616,19 +7610,19 @@
         <v>7</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7648,19 +7642,19 @@
         <v>6</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7680,19 +7674,19 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7712,19 +7706,19 @@
         <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7744,19 +7738,19 @@
         <v>13</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7776,19 +7770,19 @@
         <v>16</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7808,19 +7802,19 @@
         <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7840,19 +7834,19 @@
         <v>16</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7872,19 +7866,19 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7904,19 +7898,19 @@
         <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7936,19 +7930,19 @@
         <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -7968,19 +7962,19 @@
         <v>6</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -8000,19 +7994,19 @@
         <v>7</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -8032,19 +8026,19 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8064,19 +8058,19 @@
         <v>5</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -8096,19 +8090,19 @@
         <v>6</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -8128,19 +8122,19 @@
         <v>6</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -8160,19 +8154,19 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8192,19 +8186,19 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8224,19 +8218,19 @@
         <v>16</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -8256,19 +8250,19 @@
         <v>16</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8288,19 +8282,19 @@
         <v>16</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8320,19 +8314,19 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8352,19 +8346,19 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8384,19 +8378,19 @@
         <v>2</v>
       </c>
       <c r="C184" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="E184" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="D184" s="2" t="s">
+      <c r="F184" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="E184" s="2" t="s">
+      <c r="G184" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="F184" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="G184" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8416,19 +8410,19 @@
         <v>1</v>
       </c>
       <c r="C185" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D185" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="E185" s="2" t="s">
-        <v>392</v>
-      </c>
       <c r="F185" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8448,19 +8442,19 @@
         <v>2</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -8480,19 +8474,19 @@
         <v>1</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -8512,19 +8506,19 @@
         <v>3</v>
       </c>
       <c r="C188" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="E188" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="D188" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>399</v>
-      </c>
       <c r="F188" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -8544,19 +8538,19 @@
         <v>4</v>
       </c>
       <c r="C189" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E189" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D189" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>402</v>
-      </c>
       <c r="F189" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -8576,19 +8570,19 @@
         <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
@@ -8608,19 +8602,19 @@
         <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8640,19 +8634,19 @@
         <v>1</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8672,19 +8666,19 @@
         <v>2</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8704,19 +8698,19 @@
         <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8736,19 +8730,19 @@
         <v>15</v>
       </c>
       <c r="C195" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E195" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D195" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>415</v>
-      </c>
       <c r="F195" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8768,19 +8762,19 @@
         <v>1</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8800,19 +8794,19 @@
         <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8832,19 +8826,19 @@
         <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8864,19 +8858,19 @@
         <v>2</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8896,19 +8890,19 @@
         <v>1</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -8928,19 +8922,19 @@
         <v>4</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8960,19 +8954,19 @@
         <v>2</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -8992,19 +8986,19 @@
         <v>2</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9024,19 +9018,19 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9056,19 +9050,19 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9088,19 +9082,19 @@
         <v>3</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9120,19 +9114,19 @@
         <v>1</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D207" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E207" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9152,19 +9146,19 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9184,19 +9178,19 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9216,19 +9210,19 @@
         <v>15</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9248,19 +9242,19 @@
         <v>2</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9280,19 +9274,19 @@
         <v>3</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9312,19 +9306,19 @@
         <v>4</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9344,19 +9338,19 @@
         <v>3</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9376,19 +9370,19 @@
         <v>3</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9408,19 +9402,19 @@
         <v>3</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9440,19 +9434,19 @@
         <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9472,19 +9466,19 @@
         <v>4</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9504,19 +9498,19 @@
         <v>2</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9536,19 +9530,19 @@
         <v>4</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9568,19 +9562,19 @@
         <v>4</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9600,19 +9594,19 @@
         <v>4</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9632,19 +9626,19 @@
         <v>4</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9664,19 +9658,19 @@
         <v>2</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9696,19 +9690,19 @@
         <v>1</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9728,19 +9722,19 @@
         <v>8</v>
       </c>
       <c r="C226" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E226" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="F226" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="E226" s="2" t="s">
+      <c r="G226" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9760,19 +9754,19 @@
         <v>10</v>
       </c>
       <c r="C227" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="E227" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="D227" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="F227" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9792,19 +9786,19 @@
         <v>10</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D228" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E228" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G228" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9824,19 +9818,19 @@
         <v>10</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9856,19 +9850,19 @@
         <v>9</v>
       </c>
       <c r="C230" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E230" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D230" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>488</v>
-      </c>
       <c r="F230" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9888,19 +9882,19 @@
         <v>8</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9920,19 +9914,19 @@
         <v>9</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D232" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E232" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -9952,19 +9946,19 @@
         <v>10</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -9984,19 +9978,19 @@
         <v>10</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D234" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="E234" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -10016,19 +10010,19 @@
         <v>10</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -10048,25 +10042,25 @@
         <v>10</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>5.62</v>
+        <v>5.63</v>
       </c>
       <c r="J236" s="2" t="s">
         <v>15</v>
@@ -10080,19 +10074,19 @@
         <v>10</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
@@ -10112,19 +10106,19 @@
         <v>10</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
@@ -10144,19 +10138,19 @@
         <v>14</v>
       </c>
       <c r="C239" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E239" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="D239" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>507</v>
-      </c>
       <c r="F239" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10176,19 +10170,19 @@
         <v>10</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
@@ -10208,19 +10202,19 @@
         <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10240,19 +10234,19 @@
         <v>10</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10272,19 +10266,19 @@
         <v>9</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10304,19 +10298,19 @@
         <v>14</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10336,19 +10330,19 @@
         <v>8</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10368,19 +10362,19 @@
         <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10400,19 +10394,19 @@
         <v>9</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10432,19 +10426,19 @@
         <v>14</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10464,19 +10458,19 @@
         <v>8</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
@@ -10496,19 +10490,19 @@
         <v>9</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
@@ -10528,19 +10522,19 @@
         <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10560,19 +10554,19 @@
         <v>10</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10592,19 +10586,19 @@
         <v>10</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
@@ -10624,19 +10618,19 @@
         <v>9</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10656,19 +10650,19 @@
         <v>10</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
@@ -10688,19 +10682,19 @@
         <v>8</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10720,19 +10714,19 @@
         <v>9</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10752,19 +10746,19 @@
         <v>9</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10784,19 +10778,19 @@
         <v>8</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
@@ -10816,19 +10810,19 @@
         <v>10</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10848,19 +10842,19 @@
         <v>9</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10880,19 +10874,19 @@
         <v>9</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10912,19 +10906,19 @@
         <v>8</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
@@ -10944,19 +10938,19 @@
         <v>8</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -10976,19 +10970,19 @@
         <v>10</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -11008,19 +11002,19 @@
         <v>8</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
@@ -11040,19 +11034,19 @@
         <v>9</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11072,19 +11066,19 @@
         <v>9</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11104,19 +11098,19 @@
         <v>10</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11136,19 +11130,19 @@
         <v>10</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
@@ -11168,19 +11162,19 @@
         <v>14</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11200,19 +11194,19 @@
         <v>8</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
@@ -11232,19 +11226,19 @@
         <v>9</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
@@ -11264,19 +11258,19 @@
         <v>9</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
@@ -11296,19 +11290,19 @@
         <v>9</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
@@ -11328,19 +11322,19 @@
         <v>10</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11360,19 +11354,19 @@
         <v>14</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11392,19 +11386,19 @@
         <v>8</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
@@ -11424,19 +11418,19 @@
         <v>9</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
@@ -11456,19 +11450,19 @@
         <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11488,19 +11482,19 @@
         <v>8</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11520,19 +11514,19 @@
         <v>8</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11552,19 +11546,19 @@
         <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11584,19 +11578,19 @@
         <v>9</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
@@ -11616,19 +11610,19 @@
         <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
@@ -11648,19 +11642,19 @@
         <v>9</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
@@ -11680,19 +11674,19 @@
         <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
@@ -11712,19 +11706,19 @@
         <v>10</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
@@ -11744,19 +11738,19 @@
         <v>9</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11776,19 +11770,19 @@
         <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11808,19 +11802,19 @@
         <v>9</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11840,19 +11834,19 @@
         <v>8</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11872,19 +11866,19 @@
         <v>8</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
@@ -11904,19 +11898,19 @@
         <v>8</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -11936,19 +11930,19 @@
         <v>9</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -11968,19 +11962,19 @@
         <v>10</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
@@ -12000,19 +11994,19 @@
         <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
@@ -12032,19 +12026,19 @@
         <v>10</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12064,19 +12058,19 @@
         <v>10</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12096,19 +12090,19 @@
         <v>10</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12128,19 +12122,19 @@
         <v>10</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12160,19 +12154,19 @@
         <v>9</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
@@ -12192,19 +12186,19 @@
         <v>8</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
@@ -12224,19 +12218,19 @@
         <v>8</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
@@ -12256,19 +12250,19 @@
         <v>9</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
@@ -12288,19 +12282,19 @@
         <v>8</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12320,19 +12314,19 @@
         <v>8</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12352,19 +12346,19 @@
         <v>8</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
@@ -12384,19 +12378,19 @@
         <v>8</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12416,19 +12410,19 @@
         <v>14</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
@@ -12448,19 +12442,19 @@
         <v>8</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12480,19 +12474,19 @@
         <v>9</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12512,19 +12506,19 @@
         <v>10</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12544,19 +12538,19 @@
         <v>14</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
@@ -12576,19 +12570,19 @@
         <v>14</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
@@ -12608,19 +12602,19 @@
         <v>8</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12640,19 +12634,19 @@
         <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
@@ -12672,19 +12666,19 @@
         <v>14</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
@@ -12704,19 +12698,19 @@
         <v>10</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
@@ -12736,19 +12730,19 @@
         <v>8</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
@@ -12768,19 +12762,19 @@
         <v>9</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
@@ -12800,19 +12794,19 @@
         <v>8</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
@@ -12832,19 +12826,19 @@
         <v>9</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
@@ -12864,19 +12858,19 @@
         <v>8</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
@@ -12896,19 +12890,19 @@
         <v>8</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
@@ -12928,19 +12922,19 @@
         <v>14</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>15</v>
@@ -12960,19 +12954,19 @@
         <v>10</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>15</v>
@@ -12992,19 +12986,19 @@
         <v>9</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>15</v>
@@ -13024,19 +13018,19 @@
         <v>9</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>15</v>
@@ -13056,19 +13050,19 @@
         <v>8</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>15</v>
@@ -13088,19 +13082,19 @@
         <v>14</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>15</v>
@@ -13130,7 +13124,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -13138,50 +13132,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>
@@ -13203,21 +13197,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13226,7 +13220,7 @@
         <v>2021</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
